--- a/nablarch_sample_aws/アプリケーション方式設計書_7処理方式共通_7.14設定値管理_AWS.xlsx
+++ b/nablarch_sample_aws/アプリケーション方式設計書_7処理方式共通_7.14設定値管理_AWS.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26130"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B1B3123-067D-4D79-B40B-78BAF72E85D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36D38595-1568-4898-95CF-D83979BA81A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1245" yWindow="-120" windowWidth="27675" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -148,10 +148,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>コンポーネント設定ファイルから環境依存値を参照する</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>本システムでは、ガイドで利用が推奨されているpropertiesの形式を採用する。</t>
     <rPh sb="0" eb="1">
       <t>ホン</t>
@@ -221,10 +217,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>OS環境変数を使って環境依存値を上書きする</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>本システムでは、この仕組みを利用して実行環境ごとに設定値を切り替える方針とする。</t>
     <rPh sb="9" eb="11">
       <t>シク</t>
@@ -397,6 +389,14 @@
     <rPh sb="66" eb="68">
       <t>カンリ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://nablarch.github.io/docs/6u2/doc/application_framework/application_framework/libraries/repository.html#repository-user-environment-configuration</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://nablarch.github.io/docs/6u2/doc/application_framework/application_framework/libraries/repository.html#os</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -633,7 +633,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -756,6 +756,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1290,11 +1293,39 @@
     <row r="11" spans="1:35" s="19" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D11" s="18"/>
     </row>
-    <row r="12" spans="1:35" s="19" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:35" s="19" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D12" s="18"/>
-      <c r="E12" s="20" t="s">
-        <v>16</v>
-      </c>
+      <c r="E12" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="41"/>
+      <c r="J12" s="41"/>
+      <c r="K12" s="41"/>
+      <c r="L12" s="41"/>
+      <c r="M12" s="41"/>
+      <c r="N12" s="41"/>
+      <c r="O12" s="41"/>
+      <c r="P12" s="41"/>
+      <c r="Q12" s="41"/>
+      <c r="R12" s="41"/>
+      <c r="S12" s="41"/>
+      <c r="T12" s="41"/>
+      <c r="U12" s="41"/>
+      <c r="V12" s="41"/>
+      <c r="W12" s="41"/>
+      <c r="X12" s="41"/>
+      <c r="Y12" s="41"/>
+      <c r="Z12" s="41"/>
+      <c r="AA12" s="41"/>
+      <c r="AB12" s="41"/>
+      <c r="AC12" s="41"/>
+      <c r="AD12" s="41"/>
+      <c r="AE12" s="41"/>
+      <c r="AF12" s="41"/>
+      <c r="AG12" s="41"/>
     </row>
     <row r="13" spans="1:35" s="19" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D13" s="18"/>
@@ -1302,13 +1333,13 @@
     <row r="14" spans="1:35" s="19" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D14" s="18"/>
       <c r="E14" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:35" s="19" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D15" s="18"/>
       <c r="E15" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:35" s="19" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -1327,7 +1358,7 @@
     <row r="18" spans="4:43" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D18" s="15"/>
       <c r="E18" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F18" s="17"/>
       <c r="G18" s="17"/>
@@ -1360,7 +1391,7 @@
     </row>
     <row r="19" spans="4:43" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E19" s="21" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F19" s="17"/>
       <c r="G19" s="17"/>
@@ -1393,7 +1424,7 @@
     </row>
     <row r="20" spans="4:43" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E20" s="21" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
@@ -1457,7 +1488,7 @@
     </row>
     <row r="22" spans="4:43" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E22" s="20" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F22" s="17"/>
       <c r="G22" s="17"/>
@@ -1524,7 +1555,7 @@
     <row r="24" spans="4:43" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D24" s="17"/>
       <c r="E24" s="21" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F24" s="21"/>
       <c r="G24" s="17"/>
@@ -1558,7 +1589,7 @@
     <row r="25" spans="4:43" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D25" s="17"/>
       <c r="E25" s="21" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F25" s="21"/>
       <c r="G25" s="17"/>
@@ -1624,7 +1655,7 @@
     <row r="27" spans="4:43" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D27" s="17"/>
       <c r="E27" s="21" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F27" s="21"/>
       <c r="G27" s="17"/>
@@ -1657,7 +1688,7 @@
     </row>
     <row r="28" spans="4:43" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E28" s="21" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F28" s="17"/>
       <c r="G28" s="17"/>
@@ -1690,7 +1721,7 @@
     </row>
     <row r="29" spans="4:43" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E29" s="21" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F29" s="17"/>
       <c r="G29" s="17"/>
@@ -2141,7 +2172,8 @@
     <row r="447" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="448" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
+    <mergeCell ref="E12:AG12"/>
     <mergeCell ref="AF3:AI3"/>
     <mergeCell ref="E1:O1"/>
     <mergeCell ref="R1:X1"/>
